--- a/sample-uploads/sample_faculty.xlsx
+++ b/sample-uploads/sample_faculty.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,13 +427,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>June Arreb Danila</v>
+        <v>Edrian Lait</v>
       </c>
       <c r="B2" t="str">
-        <v>Program Head</v>
+        <v>Dean</v>
       </c>
       <c r="C2" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D2" t="str">
         <v>Active</v>
@@ -442,76 +442,76 @@
         <v>Male</v>
       </c>
       <c r="F2" t="str">
-        <v>1985-03-14</v>
+        <v>1978-08-09</v>
       </c>
       <c r="G2" t="str">
-        <v>jdanila@unc.edu.ph</v>
+        <v>edrian.lait@unc.edu.ph</v>
       </c>
       <c r="H2" t="str">
-        <v>0917 555 0101</v>
+        <v>0917 555 0119</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Alan Turing</v>
+        <v>Kristine San Lorenzo</v>
       </c>
       <c r="B3" t="str">
         <v>Program Head</v>
       </c>
       <c r="C3" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D3" t="str">
         <v>Active</v>
       </c>
       <c r="E3" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="F3" t="str">
-        <v>1982-06-23</v>
+        <v>1988-05-11</v>
       </c>
       <c r="G3" t="str">
-        <v>aturing@unc.edu.ph</v>
+        <v>kristine.sanlorenzo@unc.edu.ph</v>
       </c>
       <c r="H3" t="str">
-        <v>0917 555 0102</v>
+        <v>0917 555 0120</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Sarah Jenkins</v>
+        <v>June Arreb Danila</v>
       </c>
       <c r="B4" t="str">
-        <v>Program Head</v>
+        <v>Associate Professor</v>
       </c>
       <c r="C4" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D4" t="str">
         <v>Active</v>
       </c>
       <c r="E4" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="F4" t="str">
-        <v>1987-09-02</v>
+        <v>1985-03-14</v>
       </c>
       <c r="G4" t="str">
-        <v>sjenkins@unc.edu.ph</v>
+        <v>june.danila@unc.edu.ph</v>
       </c>
       <c r="H4" t="str">
-        <v>0917 555 0103</v>
+        <v>0917 555 0101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Thomas Bayes</v>
+        <v>Alan Turing</v>
       </c>
       <c r="B5" t="str">
         <v>Program Head</v>
       </c>
       <c r="C5" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D5" t="str">
         <v>Active</v>
@@ -520,24 +520,24 @@
         <v>Male</v>
       </c>
       <c r="F5" t="str">
-        <v>1980-11-18</v>
+        <v>1982-06-23</v>
       </c>
       <c r="G5" t="str">
-        <v>tbayes@unc.edu.ph</v>
+        <v>alan.turing@unc.edu.ph</v>
       </c>
       <c r="H5" t="str">
-        <v>0917 555 0104</v>
+        <v>0917 555 0102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Margaret Hamilton</v>
+        <v>Sarah Jenkins</v>
       </c>
       <c r="B6" t="str">
         <v>Program Head</v>
       </c>
       <c r="C6" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D6" t="str">
         <v>Active</v>
@@ -546,24 +546,24 @@
         <v>Female</v>
       </c>
       <c r="F6" t="str">
-        <v>1986-01-27</v>
+        <v>1987-09-02</v>
       </c>
       <c r="G6" t="str">
-        <v>mhamilton@unc.edu.ph</v>
+        <v>sarah.jenkins@unc.edu.ph</v>
       </c>
       <c r="H6" t="str">
-        <v>0917 555 0105</v>
+        <v>0917 555 0103</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>John Backus</v>
+        <v>Thomas Bayes</v>
       </c>
       <c r="B7" t="str">
         <v>Program Head</v>
       </c>
       <c r="C7" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D7" t="str">
         <v>Active</v>
@@ -572,50 +572,50 @@
         <v>Male</v>
       </c>
       <c r="F7" t="str">
-        <v>1979-07-05</v>
+        <v>1980-11-18</v>
       </c>
       <c r="G7" t="str">
-        <v>jbackus@unc.edu.ph</v>
+        <v>thomas.bayes@unc.edu.ph</v>
       </c>
       <c r="H7" t="str">
-        <v>0917 555 0106</v>
+        <v>0917 555 0104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Robert Noyce</v>
+        <v>Margaret Hamilton</v>
       </c>
       <c r="B8" t="str">
         <v>Program Head</v>
       </c>
       <c r="C8" t="str">
-        <v>College of Engineering</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D8" t="str">
         <v>Active</v>
       </c>
       <c r="E8" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="F8" t="str">
-        <v>1981-04-30</v>
+        <v>1986-01-27</v>
       </c>
       <c r="G8" t="str">
-        <v>rnoyce@unc.edu.ph</v>
+        <v>margaret.hamilton@unc.edu.ph</v>
       </c>
       <c r="H8" t="str">
-        <v>0917 555 0107</v>
+        <v>0917 555 0105</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Danny B. Casimero</v>
+        <v>John Backus</v>
       </c>
       <c r="B9" t="str">
-        <v>Professor</v>
+        <v>Program Head</v>
       </c>
       <c r="C9" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D9" t="str">
         <v>Active</v>
@@ -624,24 +624,24 @@
         <v>Male</v>
       </c>
       <c r="F9" t="str">
-        <v>1976-05-22</v>
+        <v>1979-07-05</v>
       </c>
       <c r="G9" t="str">
-        <v>dcasimero@unc.edu.ph</v>
+        <v>john.backus@unc.edu.ph</v>
       </c>
       <c r="H9" t="str">
-        <v>0918 555 0108</v>
+        <v>0917 555 0106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Dennis Ignacio</v>
+        <v>Robert Noyce</v>
       </c>
       <c r="B10" t="str">
-        <v>Associate Professor</v>
+        <v>Program Head</v>
       </c>
       <c r="C10" t="str">
-        <v>College of Computer Studies</v>
+        <v>College of Engineering</v>
       </c>
       <c r="D10" t="str">
         <v>Active</v>
@@ -650,24 +650,24 @@
         <v>Male</v>
       </c>
       <c r="F10" t="str">
-        <v>1984-02-19</v>
+        <v>1981-04-30</v>
       </c>
       <c r="G10" t="str">
-        <v>dignacio@unc.edu.ph</v>
+        <v>robert.noyce@unc.edu.ph</v>
       </c>
       <c r="H10" t="str">
-        <v>0918 555 0109</v>
+        <v>0917 555 0107</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Michael R. Lee</v>
+        <v>Danny B. Casimero</v>
       </c>
       <c r="B11" t="str">
-        <v>Associate Professor</v>
+        <v>Professor</v>
       </c>
       <c r="C11" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D11" t="str">
         <v>Active</v>
@@ -676,102 +676,102 @@
         <v>Male</v>
       </c>
       <c r="F11" t="str">
-        <v>1983-09-15</v>
+        <v>1976-05-22</v>
       </c>
       <c r="G11" t="str">
-        <v>mlee@unc.edu.ph</v>
+        <v>danny.casimero@unc.edu.ph</v>
       </c>
       <c r="H11" t="str">
-        <v>0918 555 0110</v>
+        <v>0918 555 0108</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Marceline Avila</v>
+        <v>Dennis Ignacio</v>
       </c>
       <c r="B12" t="str">
-        <v>Assistant Professor</v>
+        <v>Associate Professor</v>
       </c>
       <c r="C12" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D12" t="str">
         <v>Active</v>
       </c>
       <c r="E12" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="F12" t="str">
-        <v>1990-08-12</v>
+        <v>1984-02-19</v>
       </c>
       <c r="G12" t="str">
-        <v>mavila@unc.edu.ph</v>
+        <v>dennis.ignacio@unc.edu.ph</v>
       </c>
       <c r="H12" t="str">
-        <v>0918 555 0111</v>
+        <v>0918 555 0109</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Saige Fuentes</v>
+        <v>Michael R. Lee</v>
       </c>
       <c r="B13" t="str">
-        <v>Assistant Professor</v>
+        <v>Associate Professor</v>
       </c>
       <c r="C13" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D13" t="str">
         <v>Active</v>
       </c>
       <c r="E13" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="F13" t="str">
-        <v>1991-03-28</v>
+        <v>1983-09-15</v>
       </c>
       <c r="G13" t="str">
-        <v>sfuentes@unc.edu.ph</v>
+        <v>michael.lee@unc.edu.ph</v>
       </c>
       <c r="H13" t="str">
-        <v>0918 555 0112</v>
+        <v>0918 555 0110</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Harold T. Lim</v>
+        <v>Marceline Avila</v>
       </c>
       <c r="B14" t="str">
         <v>Assistant Professor</v>
       </c>
       <c r="C14" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D14" t="str">
         <v>Active</v>
       </c>
       <c r="E14" t="str">
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="F14" t="str">
-        <v>1988-11-21</v>
+        <v>1990-08-12</v>
       </c>
       <c r="G14" t="str">
-        <v>hlim@unc.edu.ph</v>
+        <v>marceline.avila@unc.edu.ph</v>
       </c>
       <c r="H14" t="str">
-        <v>0918 555 0113</v>
+        <v>0918 555 0111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Bianca G. Reyes</v>
+        <v>Saige Fuentes</v>
       </c>
       <c r="B15" t="str">
-        <v>Instructor</v>
+        <v>Assistant Professor</v>
       </c>
       <c r="C15" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D15" t="str">
         <v>Active</v>
@@ -780,24 +780,24 @@
         <v>Female</v>
       </c>
       <c r="F15" t="str">
-        <v>1993-12-03</v>
+        <v>1991-03-28</v>
       </c>
       <c r="G15" t="str">
-        <v>breyes@unc.edu.ph</v>
+        <v>saige.fuentes@unc.edu.ph</v>
       </c>
       <c r="H15" t="str">
-        <v>0918 555 0114</v>
+        <v>0918 555 0112</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Bowen Higgins</v>
+        <v>Harold T. Lim</v>
       </c>
       <c r="B16" t="str">
-        <v>Instructor</v>
+        <v>Assistant Professor</v>
       </c>
       <c r="C16" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D16" t="str">
         <v>Active</v>
@@ -806,24 +806,24 @@
         <v>Male</v>
       </c>
       <c r="F16" t="str">
-        <v>1994-10-09</v>
+        <v>1988-11-21</v>
       </c>
       <c r="G16" t="str">
-        <v>bhiggins@unc.edu.ph</v>
+        <v>harold.lim@unc.edu.ph</v>
       </c>
       <c r="H16" t="str">
-        <v>0918 555 0115</v>
+        <v>0918 555 0113</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Christine A. Dizon</v>
+        <v>Bianca G. Reyes</v>
       </c>
       <c r="B17" t="str">
         <v>Instructor</v>
       </c>
       <c r="C17" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D17" t="str">
         <v>Active</v>
@@ -832,70 +832,200 @@
         <v>Female</v>
       </c>
       <c r="F17" t="str">
-        <v>1992-06-07</v>
+        <v>1993-12-03</v>
       </c>
       <c r="G17" t="str">
-        <v>cdizon@unc.edu.ph</v>
+        <v>bianca.reyes@unc.edu.ph</v>
       </c>
       <c r="H17" t="str">
-        <v>0918 555 0116</v>
+        <v>0918 555 0114</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Gregorio P. Santos</v>
+        <v>Bowen Higgins</v>
       </c>
       <c r="B18" t="str">
-        <v>Professor</v>
+        <v>Instructor</v>
       </c>
       <c r="C18" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D18" t="str">
-        <v>On Leave</v>
+        <v>Active</v>
       </c>
       <c r="E18" t="str">
         <v>Male</v>
       </c>
       <c r="F18" t="str">
-        <v>1975-01-10</v>
+        <v>1994-10-09</v>
       </c>
       <c r="G18" t="str">
-        <v>gsantos@unc.edu.ph</v>
+        <v>bowen.higgins@unc.edu.ph</v>
       </c>
       <c r="H18" t="str">
-        <v>0919 555 0117</v>
+        <v>0918 555 0115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Maria Elena Cruz</v>
+        <v>Christine A. Dizon</v>
       </c>
       <c r="B19" t="str">
         <v>Instructor</v>
       </c>
       <c r="C19" t="str">
-        <v>College of Computer Studies</v>
+        <v>School of Computer &amp; Information Sciences</v>
       </c>
       <c r="D19" t="str">
-        <v>Inactive</v>
+        <v>Active</v>
       </c>
       <c r="E19" t="str">
         <v>Female</v>
       </c>
       <c r="F19" t="str">
+        <v>1992-06-07</v>
+      </c>
+      <c r="G19" t="str">
+        <v>christine.dizon@unc.edu.ph</v>
+      </c>
+      <c r="H19" t="str">
+        <v>0918 555 0116</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Olivia Vance</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Instructor</v>
+      </c>
+      <c r="C20" t="str">
+        <v>School of Computer &amp; Information Sciences</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F20" t="str">
+        <v>1990-02-21</v>
+      </c>
+      <c r="G20" t="str">
+        <v>olivia.vance@unc.edu.ph</v>
+      </c>
+      <c r="H20" t="str">
+        <v>0918 555 0121</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Monica Norton</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Instructor</v>
+      </c>
+      <c r="C21" t="str">
+        <v>School of Computer &amp; Information Sciences</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F21" t="str">
+        <v>1995-07-17</v>
+      </c>
+      <c r="G21" t="str">
+        <v>monica.norton@unc.edu.ph</v>
+      </c>
+      <c r="H21" t="str">
+        <v>0918 555 0122</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Gregorio P. Santos</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Professor</v>
+      </c>
+      <c r="C22" t="str">
+        <v>School of Computer &amp; Information Sciences</v>
+      </c>
+      <c r="D22" t="str">
+        <v>On Leave</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F22" t="str">
+        <v>1975-01-10</v>
+      </c>
+      <c r="G22" t="str">
+        <v>gregorio.santos@unc.edu.ph</v>
+      </c>
+      <c r="H22" t="str">
+        <v>0919 555 0117</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Maria Elena Cruz</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Instructor</v>
+      </c>
+      <c r="C23" t="str">
+        <v>School of Computer &amp; Information Sciences</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Inactive</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F23" t="str">
         <v>1989-04-16</v>
       </c>
-      <c r="G19" t="str">
-        <v>mecruz@unc.edu.ph</v>
-      </c>
-      <c r="H19" t="str">
+      <c r="G23" t="str">
+        <v>maria.cruz@unc.edu.ph</v>
+      </c>
+      <c r="H23" t="str">
         <v>0919 555 0118</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Marco Dela Rosa</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Instructor</v>
+      </c>
+      <c r="C24" t="str">
+        <v>School of Computer &amp; Information Sciences</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F24" t="str">
+        <v>1992-09-25</v>
+      </c>
+      <c r="G24" t="str">
+        <v>marco.delarosa@gmail.com</v>
+      </c>
+      <c r="H24" t="str">
+        <v>0919 555 0123</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H24"/>
   </ignoredErrors>
 </worksheet>
 </file>